--- a/光伏配储项目/电价数据/2026/胪岗站.xlsx
+++ b/光伏配储项目/电价数据/2026/胪岗站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.32969</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5228700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.25164</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.24662</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07267</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17038</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.92262</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.01826</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.49841</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.6244700000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.00877</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.07394</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.9268</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.87658</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.04995</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.52898</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54772</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.12373</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5519299999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.5488999999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.52888</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34943</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.54089</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.96938</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.33883</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.61434</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.65023</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61094</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.66701</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54941</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.7300800000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.52522</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.56824</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.5328200000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.36436</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.86876</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.99478</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.9043600000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.68925</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.9659099999999999</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.9214</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.0229</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.97287</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.90591</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7324700000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.8055099999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.7110599999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8479</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76979</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.87982</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.72736</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.30464</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.6786</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6601900000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.41406</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33183</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.45274</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.43925</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.14818</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19176</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.10119</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6173500000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.52711</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6164400000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.6147899999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.67257</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.62382</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6916</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.71149</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7443099999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.66426</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.64354</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.62515</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.54904</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45911</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.13376</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45836</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51179</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52375</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.62166</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.56811</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6425700000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.71027</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.53592</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70689</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51309</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5277200000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.51002</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6631900000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6184299999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6080399999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.58282</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.48667</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47286</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55702</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5234800000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33851</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40713</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.03381</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.79771</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.23037</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.20046</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66987</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.22138</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14363</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02664</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2566000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10342</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02941</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31887</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25584</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.18352</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.25758</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19841</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.10204</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04427</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.24594</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25224</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22078</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18141</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25355</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20815</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.11311</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04989</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06064</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31673</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.12932</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78095</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6596599999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57436</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.43509</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5624199999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.76048</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.25195</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.20187</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.15139</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18604</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26473</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.66339</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.18482</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.22894</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.19209</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.02473</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.44979</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.06944</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.19052</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.14506</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.19347</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.22466</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.20801</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.20966</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.02563</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.02409</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.02592</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.02149</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.02303</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.02711</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.02999</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.22184</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.20653</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.16896</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.20392</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.19262</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.20499</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.2082</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.18285</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.19786</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.20115</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.18766</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.20411</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.21535</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.21243</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.20198</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.22015</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.19732</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.19304</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.21709</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.23577</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.20197</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.19865</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.20497</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.13131</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.61161</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.14612</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.13369</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.12327</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.15234</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.21602</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.15214</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.13242</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.23692</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.23208</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.20908</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.25129</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.23338</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.22245</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.22477</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.25157</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.04039</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.07526999999999999</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.04161</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.25159</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.00464</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.22179</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.24689</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.10012</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.22696</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.15944</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.07843000000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.23344</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.23065</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.10019</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.10859</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.26007</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.03288</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.08643000000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.18486</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.24129</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.21129</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.24299</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.21737</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.23861</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.20946</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.17196</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.21352</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.19794</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.18557</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.10805</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.14934</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.14035</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19132</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.11904</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.17935</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.19625</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.19415</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.22395</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.01099</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.00034</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.08996</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.21724</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03471</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19748</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.03531</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.05656</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.05522999999999999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.20761</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.02506</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.18934</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.11914</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.19347</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.22397</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.20746</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.19609</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.21338</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24786</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24935</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26754</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.22021</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24697</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.24355</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25405</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28461</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30342</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.8176599999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.5524600000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.44019</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49415</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.52889</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.47297</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.20584</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68669</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47589</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.15133</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.23929</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.14342</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20576</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27324</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27318</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19958</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19688</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16213</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23937</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19662</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20227</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.12498</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20946</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17569</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16677</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.19645</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.26723</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.27286</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.27216</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.26276</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24413</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.25964</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.20887</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23576</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.26519</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.25751</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.25367</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.11428</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.09927</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23996</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31999</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27679</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.50785</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.47456</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21395</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29901</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.52887</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.50162</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.54308</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6671</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31648</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46979</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58173</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.66872</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.62975</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.18699</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.26352</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.56916</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64401</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32359</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27557</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.61866</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.26922</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.13777</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.11872</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.11537</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.12735</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.18647</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.16846</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.12443</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.23127</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.26687</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.12084</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.06125</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.12092</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.11355</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.11096</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.22567</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21483</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21547</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17577</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01163</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17598</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.0008900000000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01023</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16497</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20295</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16723</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17005</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17288</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00919</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.009010000000000001</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01489</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18701</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18846</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15717</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03074</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.18784</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.01321</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.16709</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23677</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.19737</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.08646</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04506</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.00203</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.03306</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24943</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.09744</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.03376</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.06670000000000001</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.04607</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.05534</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.05973</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.08444</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.08638999999999999</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.19104</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.19243</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.05282</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.23327</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.19716</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.0373</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.17288</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.08554</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.10058</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.08434999999999999</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.04715999999999999</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22706</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.13621</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.14791</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25231</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.19976</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24565</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.14475</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.15424</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.12942</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.11553</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.16866</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23322</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05503</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19114</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18809</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.0008100000000000001</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20692</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22705</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21897</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00305</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00304</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20163</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01064</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01009</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00181</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03836999999999999</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.05565999999999999</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02708</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.02269</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25271</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04222</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.15535</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.23824</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25149</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26434</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.00373</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25688</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26939</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27297</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03679</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17856</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17302</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17749</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.01767</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17074</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15922</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.04752</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.01931</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20302</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04011</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85898</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86172</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09304000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06876</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.58236</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.46317</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.6417999999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.7167899999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.50854</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.29428</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.6130599999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.6112799999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.6708099999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31103</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20082</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25193</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22135</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17595</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20467</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17024</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17301</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.01821</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19129</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23989</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24843</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25817</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29492</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.48865</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6557200000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.57862</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.65595</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.09026000000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42876</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20338</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31922</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.14885</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.11316</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.19214</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.02797</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.61226</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55169</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.48835</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32381</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01853</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27318</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5744900000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20047</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43562</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5470700000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24765</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.19391</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.01138</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.23662</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.11869</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.18172</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.18727</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.06515</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.17527</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.25538</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32802</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.57296</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.20793</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.11978</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.12564</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.24635</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.23431</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.15083</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33968</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14607</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12157</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18823</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16165</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20467</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.06369</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.02871</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>-0.00482</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.12538</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.08551</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.20608</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.20249</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.24425</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.22721</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36931</v>
       </c>
     </row>
   </sheetData>
